--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487089_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487089_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1966</v>
+        <v>1.4226</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4722</v>
+        <v>0.5911</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7244</v>
+        <v>0.8315</v>
       </c>
       <c r="G2" t="n">
         <v>0.5723</v>
@@ -610,13 +610,13 @@
         <v>0.386</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0476</v>
+        <v>0.1785</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.119</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1785</v>
       </c>
       <c r="V2" t="n">
         <v>0.2859</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7267</v>
+        <v>0.0318</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7773</v>
+        <v>2.6161</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.504</v>
+        <v>-2.5843</v>
       </c>
       <c r="G3" t="n">
         <v>-4.4061</v>
@@ -688,13 +688,13 @@
         <v>0.965</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2584</v>
+        <v>1.0169</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5089</v>
+        <v>0.3299</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7674</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>2.4559</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8975</v>
+        <v>-0.4652</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.1214</v>
+        <v>-1.7427</v>
       </c>
       <c r="F4" t="n">
-        <v>1.224</v>
+        <v>1.2775</v>
       </c>
       <c r="G4" t="n">
         <v>0.2973</v>
@@ -766,13 +766,13 @@
         <v>0.386</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0211</v>
+        <v>0.4534</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5354</v>
+        <v>-0.1566</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5565</v>
+        <v>0.6101</v>
       </c>
       <c r="V4" t="n">
         <v>0.3281</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9404</v>
+        <v>-1.0028</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.975</v>
+        <v>-0.7966</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0347</v>
+        <v>-0.2063</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4373</v>
@@ -844,13 +844,13 @@
         <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0337</v>
+        <v>-0.0288</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7139</v>
+        <v>-0.5354</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.0422</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.5877</v>
+        <v>-3.0834</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9132</v>
+        <v>1.6316</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.5009</v>
+        <v>-4.7151</v>
       </c>
       <c r="G6" t="n">
         <v>-3.6634</v>
@@ -922,13 +922,13 @@
         <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3809</v>
+        <v>1.8851</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3617</v>
+        <v>1.0801</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0192</v>
+        <v>0.805</v>
       </c>
       <c r="V6" t="n">
         <v>-1.8842</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.0371</v>
+        <v>-4.5509</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1051</v>
+        <v>-2.105</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.932</v>
+        <v>-2.4459</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3152</v>
+        <v>-4.4471</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4005</v>
+        <v>2.7509</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9147</v>
+        <v>-7.198</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7012</v>
+        <v>-0.977</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0314</v>
+        <v>4.1603</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7326</v>
+        <v>-5.1373</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0164</v>
+        <v>-3.4701</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3691</v>
+        <v>-1.4094</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6473</v>
+        <v>-2.0607</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.4741</v>
+        <v>-3.8602</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8602</v>
+        <v>-4.8252</v>
       </c>
       <c r="R7" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>4.266</v>
+        <v>0.4006</v>
       </c>
       <c r="T7" t="n">
-        <v>3.0538</v>
+        <v>0.0556</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2122</v>
+        <v>0.345</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5138</v>
+        <v>3.3558</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.6417</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5138</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.6544</v>
+        <v>-5.2082</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.403</v>
+        <v>-0.9836</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2514</v>
+        <v>-4.2246</v>
       </c>
       <c r="G8" t="n">
         <v>-3.1918</v>
@@ -1078,13 +1078,13 @@
         <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8137</v>
+        <v>-0.3675</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7139</v>
+        <v>-0.2945</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0998</v>
+        <v>-0.0731</v>
       </c>
       <c r="V8" t="n">
         <v>-1.842</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FRECHILLA GOMEZ</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.0937</v>
+        <v>-5.2214</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.668</v>
+        <v>-1.8075</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.4257</v>
+        <v>-3.4138</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.137</v>
+        <v>-2.3152</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8825</v>
+        <v>-1.4005</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.2545</v>
+        <v>-0.9147</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0996</v>
+        <v>0.7012</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4399</v>
+        <v>-0.0314</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6597</v>
+        <v>0.7326</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.0373</v>
+        <v>-3.0164</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4426</v>
+        <v>-1.3691</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.5948</v>
+        <v>-1.6473</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3511</v>
+        <v>-3.4741</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R9" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6802</v>
+        <v>2.0818</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3617</v>
+        <v>1.3514</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6815</v>
+        <v>0.7304</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>A. FRECHILLA GOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.7599</v>
+        <v>-6.2335</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8857</v>
+        <v>-2.2094</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8742</v>
+        <v>-4.0241</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.4471</v>
+        <v>-5.137</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7509</v>
+        <v>-1.8825</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.198</v>
+        <v>-3.2545</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.977</v>
+        <v>-1.0996</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1603</v>
+        <v>-0.4399</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.1373</v>
+        <v>-0.6597</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.4701</v>
+        <v>-4.0373</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4094</v>
+        <v>-1.4426</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0607</v>
+        <v>-2.5948</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.8602</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8252</v>
+        <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8085</v>
+        <v>0.5404</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7251</v>
+        <v>0.8203</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0833</v>
+        <v>-0.28</v>
       </c>
       <c r="V10" t="n">
-        <v>3.3558</v>
+        <v>-0.2859</v>
       </c>
       <c r="W10" t="n">
-        <v>3.6417</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.2859</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-25.5008</v>
+        <v>-24.311</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9955</v>
+        <v>-4.806</v>
       </c>
       <c r="F11" t="n">
         <v>-19.5051</v>
@@ -1291,13 +1291,13 @@
         <v>-1.1656</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.477399999999999</v>
+        <v>-2.4774</v>
       </c>
       <c r="M11" t="n">
         <v>-19.0851</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.746599999999999</v>
+        <v>-6.746600000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-12.3385</v>
@@ -1312,19 +1312,19 @@
         <v>4.825</v>
       </c>
       <c r="S11" t="n">
-        <v>4.970500000000001</v>
+        <v>6.1604</v>
       </c>
       <c r="T11" t="n">
-        <v>1.461</v>
+        <v>2.6508</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5096</v>
+        <v>3.5095</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9419999999999997</v>
+        <v>0.9419999999999993</v>
       </c>
       <c r="W11" t="n">
-        <v>9.697100000000001</v>
+        <v>9.697099999999999</v>
       </c>
       <c r="X11" t="n">
         <v>-8.754899999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.2906</v>
+        <v>8.775</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6878</v>
+        <v>5.788</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6028</v>
+        <v>2.9871</v>
       </c>
       <c r="G12" t="n">
         <v>5.8715</v>
@@ -1390,13 +1390,13 @@
         <v>2.1231</v>
       </c>
       <c r="S12" t="n">
-        <v>0.068</v>
+        <v>-0.4475</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5221</v>
+        <v>-0.422</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5901999999999999</v>
+        <v>-0.0255</v>
       </c>
       <c r="V12" t="n">
         <v>1.228</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.1623</v>
+        <v>7.6741</v>
       </c>
       <c r="E13" t="n">
-        <v>8.5799</v>
+        <v>6.8775</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5825</v>
+        <v>0.7966</v>
       </c>
       <c r="G13" t="n">
         <v>4.4112</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8091</v>
+        <v>-0.6792</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7913</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9823</v>
+        <v>-0.7681</v>
       </c>
       <c r="V13" t="n">
         <v>2.784</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6</v>
+        <v>4.8538</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3384</v>
+        <v>2.5387</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2616</v>
+        <v>2.3151</v>
       </c>
       <c r="G14" t="n">
         <v>3.9011</v>
@@ -1546,13 +1546,13 @@
         <v>1.7371</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.973</v>
+        <v>-0.7192</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5221</v>
+        <v>-0.3219</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4508</v>
+        <v>-0.3973</v>
       </c>
       <c r="V14" t="n">
         <v>0.8999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.829</v>
+        <v>3.8022</v>
       </c>
       <c r="E15" t="n">
         <v>1.2899</v>
       </c>
       <c r="F15" t="n">
-        <v>2.539</v>
+        <v>2.5123</v>
       </c>
       <c r="G15" t="n">
         <v>1.7498</v>
@@ -1624,13 +1624,13 @@
         <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4422</v>
+        <v>0.4154</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3437</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7859</v>
+        <v>0.7591</v>
       </c>
       <c r="V15" t="n">
         <v>0.2859</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9274</v>
+        <v>3.669</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5958</v>
+        <v>4.0965</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6684</v>
+        <v>-0.4275</v>
       </c>
       <c r="G16" t="n">
         <v>4.8699</v>
@@ -1702,13 +1702,13 @@
         <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2586</v>
+        <v>-1.517</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8328</v>
+        <v>-0.3321</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4258</v>
+        <v>-1.1849</v>
       </c>
       <c r="V16" t="n">
         <v>-1.228</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7107</v>
+        <v>0.6572</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0238</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7345</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3726</v>
@@ -1780,13 +1780,13 @@
         <v>0.386</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0833</v>
+        <v>0.0297</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2974</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3807</v>
+        <v>0.3272</v>
       </c>
       <c r="V17" t="n">
         <v>0.614</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3487</v>
+        <v>0.5222</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9659</v>
+        <v>1.1661</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6172</v>
+        <v>-0.6439</v>
       </c>
       <c r="G18" t="n">
         <v>1.1939</v>
@@ -1858,13 +1858,13 @@
         <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1963</v>
+        <v>-0.0228</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5949</v>
+        <v>-0.3946</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3986</v>
+        <v>0.3718</v>
       </c>
       <c r="V18" t="n">
         <v>-1.228</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>W. DIAZ GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.0864</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4861</v>
+        <v>-0.1835</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4438</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6187</v>
+        <v>0.4611</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8682</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7504</v>
+        <v>0.3713</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6514</v>
+        <v>0.4402</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0088</v>
+        <v>-0.3573</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.7976</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0328</v>
+        <v>0.0209</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1406</v>
+        <v>0.4472</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1078</v>
+        <v>-0.4263</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8574</v>
+        <v>-0.0337</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1303</v>
+        <v>-0.2726</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7271</v>
+        <v>0.2389</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2702</v>
+        <v>-0.8999</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0422</v>
+        <v>0.614</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.228</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. DIAZ GONZALEZ</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9351</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6842</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2509</v>
+        <v>-0.6044</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4611</v>
+        <v>1.6187</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.8682</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3713</v>
+        <v>0.7504</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4402</v>
+        <v>1.6514</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3573</v>
+        <v>1.0088</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7976</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0209</v>
+        <v>-0.0328</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4472</v>
+        <v>-0.1406</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4263</v>
+        <v>0.1078</v>
       </c>
       <c r="P20" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8824</v>
+        <v>-1.6174</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7733</v>
+        <v>-0.7297</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1091</v>
+        <v>-0.8877</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8999</v>
+        <v>-1.2702</v>
       </c>
       <c r="W20" t="n">
-        <v>0.614</v>
+        <v>-0.0422</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5138</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9568</v>
+        <v>-2.1303</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5613</v>
+        <v>-1.7616</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3955</v>
+        <v>-0.3687</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8702</v>
@@ -2170,13 +2170,13 @@
         <v>0.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0866</v>
+        <v>-0.2601</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0462</v>
+        <v>-0.2465</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0403</v>
+        <v>-0.0136</v>
       </c>
       <c r="V22" t="n">
         <v>-0.614</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>25.5009</v>
+        <v>25.5008</v>
       </c>
       <c r="E23" t="n">
         <v>19.505</v>
       </c>
       <c r="F23" t="n">
-        <v>5.995800000000002</v>
+        <v>5.995800000000001</v>
       </c>
       <c r="G23" t="n">
         <v>22.7282</v>
@@ -2248,13 +2248,13 @@
         <v>13.5107</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.970699999999999</v>
+        <v>-4.970799999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.5095</v>
+        <v>-3.5096</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.461</v>
+        <v>-1.4611</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9421000000000007</v>
